--- a/results/Int All Data -0.4/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_7_permute.xlsx
@@ -440,717 +440,717 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8145858267261765</v>
+        <v>0.8120333411410621</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8137708281861149</v>
+        <v>0.8091351229075554</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8148577602941696</v>
+        <v>0.8087769567184437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8139601388706175</v>
+        <v>0.8095715000786121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8280397199485332</v>
+        <v>0.8186820767702956</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8287560523267566</v>
+        <v>0.8186820767702956</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8294723847049801</v>
+        <v>0.8146969264287341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8289577965519787</v>
+        <v>0.8098061330244468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8251326779119352</v>
+        <v>0.8063933266379385</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8232058801823801</v>
+        <v>0.8059898381874946</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8196037631113693</v>
+        <v>0.7990655592526399</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8259147877313842</v>
+        <v>0.7992219812165298</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8218061041465458</v>
+        <v>0.7979004161626404</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8218061041465458</v>
+        <v>0.7961877961990265</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8234858353895469</v>
+        <v>0.7976080274147541</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8244039119929922</v>
+        <v>0.7976080274147541</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8163554003279245</v>
+        <v>0.7916507570823053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8177222876431461</v>
+        <v>0.7953354970368065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8055731140324138</v>
+        <v>0.7967681617932535</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8036916385641908</v>
+        <v>0.7867395084981246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8030535171679122</v>
+        <v>0.7870976746872362</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7965780489448335</v>
+        <v>0.7890653827765781</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7990852122686158</v>
+        <v>0.7866532758770058</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7990852122686158</v>
+        <v>0.7889258062549533</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7990852122686158</v>
+        <v>0.7904491155340647</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8029468293669002</v>
+        <v>0.7910419146690111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.797697869773501</v>
+        <v>0.7871020865887819</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7950342844858289</v>
+        <v>0.7912436588942331</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8019256747000709</v>
+        <v>0.7912436588942331</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8040746718347414</v>
+        <v>0.7900456270836208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8005178770250627</v>
+        <v>0.7912889811555652</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8017487975562878</v>
+        <v>0.7910872369303432</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8020287527634546</v>
+        <v>0.7959575751547374</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7964216269809439</v>
+        <v>0.7940103222452889</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7974961255482791</v>
+        <v>0.7920506357951209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7991963119711735</v>
+        <v>0.7920506357951209</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7835152106322014</v>
+        <v>0.786418642931171</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7863600849652022</v>
+        <v>0.777777332131157</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7860019187760904</v>
+        <v>0.7756283349964865</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7824451239664117</v>
+        <v>0.7764184664551093</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7869368408218009</v>
+        <v>0.7771925546353844</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7888058827493045</v>
+        <v>0.7718324953394275</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7773072640755703</v>
+        <v>0.7753812685099324</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7835320560744665</v>
+        <v>0.7710174967993659</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7769739649678975</v>
+        <v>0.7706513089710804</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7771757091931193</v>
+        <v>0.7712112193854141</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7746436787878983</v>
+        <v>0.7681441456472982</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7759945228247721</v>
+        <v>0.7757029362408032</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7693582207362581</v>
+        <v>0.7696923220078484</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7685183551147576</v>
+        <v>0.7649535386659052</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7658218811064728</v>
+        <v>0.7649988609272373</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7624872857019095</v>
+        <v>0.7694657107011875</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7638008291166249</v>
+        <v>0.7694657107011875</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7765837122220903</v>
+        <v>0.7689058002868538</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7765055012401454</v>
+        <v>0.7689058002868538</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7751963697269755</v>
+        <v>0.7585643030639453</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7751963697269755</v>
+        <v>0.7568312279204381</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7709970416194727</v>
+        <v>0.7538423651642672</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7709970416194727</v>
+        <v>0.7546369085244355</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7728003061057509</v>
+        <v>0.7546369085244355</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7736730604478641</v>
+        <v>0.7546369085244355</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7735619607453066</v>
+        <v>0.7599516455590601</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7817749160134378</v>
+        <v>0.7524301555877134</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7820095489592725</v>
+        <v>0.7447025094895992</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7760691240690888</v>
+        <v>0.7455876973724318</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.772845628367083</v>
+        <v>0.6968337788016954</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7704166760252458</v>
+        <v>0.6940759392537309</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7700585098361339</v>
+        <v>0.6962746705512792</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7694203884398554</v>
+        <v>0.7010872529736216</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7269718793417121</v>
+        <v>0.6989711445595639</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7215664977844233</v>
+        <v>0.7120961505757932</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7175155700016365</v>
+        <v>0.7192967749801866</v>
       </c>
     </row>
     <row r="74">
@@ -1160,287 +1160,287 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7116613777325713</v>
+        <v>0.7220305496106296</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7089649037242867</v>
+        <v>0.7170571333228517</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7056960857609488</v>
+        <v>0.7138665263414588</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6927487590524197</v>
+        <v>0.7065876909551205</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6562655419258994</v>
+        <v>0.7186301767648409</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6562655419258994</v>
+        <v>0.7170535235852236</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6557473440352695</v>
+        <v>0.724439848936491</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6483822760278126</v>
+        <v>0.7275273778545003</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6450352470825298</v>
+        <v>0.7359091886272409</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6152914101079071</v>
+        <v>0.7293226207016046</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6230724001065273</v>
+        <v>0.7355020904391687</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6234634550162519</v>
+        <v>0.7253045816394306</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.636834725355118</v>
+        <v>0.7203560324330915</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6362748149407843</v>
+        <v>0.7023037345543338</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6201120141694234</v>
+        <v>0.6997512489692194</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6025582611653195</v>
+        <v>0.6949430784484225</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5932006179870819</v>
+        <v>0.6520589943431401</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.589281245086746</v>
+        <v>0.6305485678165419</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5702779818839301</v>
+        <v>0.630470356834597</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5702779818839301</v>
+        <v>0.620750135565702</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5682854067131494</v>
+        <v>0.6346075172385026</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5689110945687086</v>
+        <v>0.6327260417702795</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5725132116397192</v>
+        <v>0.6276006154201574</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5626205251285868</v>
+        <v>0.5621344137946525</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5470922360158764</v>
+        <v>0.5532789252286969</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5425471752599813</v>
+        <v>0.5563832995889713</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.545568926736765</v>
+        <v>0.5530611377251273</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.549541643537607</v>
+        <v>0.5543000798955262</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5372324382253567</v>
+        <v>0.5524310379680225</v>
       </c>
     </row>
     <row r="103">
@@ -1450,537 +1450,537 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5461288371510988</v>
+        <v>0.5533162258508553</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5469562692318799</v>
+        <v>0.5492075422660168</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5439016290344835</v>
+        <v>0.5492075422660168</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5489692995825539</v>
+        <v>0.5443584613854333</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5507725640688321</v>
+        <v>0.5418352547833034</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5265452083540559</v>
+        <v>0.5362610177214052</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5332472878837953</v>
+        <v>0.5362610177214052</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5321727893164601</v>
+        <v>0.5297811375967811</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5354291737390785</v>
+        <v>0.5193614293919276</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5335849988930138</v>
+        <v>0.5193614293919276</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5376812489371329</v>
+        <v>0.5213993268240406</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5273477733533981</v>
+        <v>0.5213993268240406</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5267878629390644</v>
+        <v>0.5213993268240406</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5237003340210552</v>
+        <v>0.5007945433601684</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5230826678046698</v>
+        <v>0.5007945433601684</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5374422040897525</v>
+        <v>0.5004363771710567</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.536252193918314</v>
+        <v>0.5007163323782235</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5324234655406425</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5327487430091414</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5381256477473633</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5384056029545301</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5167965102660937</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5181509640405959</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5190237183827092</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.514503524708253</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5113253512675795</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5118728281411937</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5049236821249001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5041291387647318</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5110658512403058</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5113333729067533</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5108765405558033</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5116710839159717</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5116710839159717</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5098020419884681</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5096127313039656</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5050801040887899</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5064674465839047</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5080192326820832</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5080192326820832</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5056684913221907</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5056684913221907</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5058951026288516</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5031942167190212</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5026343063046875</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5026343063046875</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5035319277282397</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5017455086842266</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5017455086842266</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5015437644590046</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5009509653240581</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5017001864228944</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5021116965125121</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5021116965125121</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
